--- a/Pruebas calificadas/COLEGIO LAS MARGARITAS-501_Ajustado_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO LAS MARGARITAS-501_Ajustado_CALIFICADO.xlsx
@@ -10845,7 +10845,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1141348754</t>
+          <t>1141349754</t>
         </is>
       </c>
       <c r="F42" s="2" t="n">
@@ -11098,7 +11098,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1141348754</t>
+          <t>1141349754</t>
         </is>
       </c>
       <c r="F43" s="2" t="n">
